--- a/Pitrudosha and Finance.xlsx
+++ b/Pitrudosha and Finance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aksha\Desktop\Kareer Studio\Astrology\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AD899D3-B90F-4E9D-B6D1-3A6BB52FED33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{474E1F5A-B943-4C61-907B-0B538E1A9B9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{4F826109-A708-48E5-B83E-FE433EC4C9BA}"/>
   </bookViews>
